--- a/artfynd/A 50174-2020 artfynd.xlsx
+++ b/artfynd/A 50174-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50174-2020 artfynd.xlsx
+++ b/artfynd/A 50174-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3357,119 +3357,6 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>111356411</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Gyljberget, nord ost, Hls</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>551737</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6765756</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Bollnäs</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Bollnäs</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2023-07-30</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2023-07-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Enar Gesslin</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Enar Gesslin</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
